--- a/spreadsheets/lists.xlsx
+++ b/spreadsheets/lists.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152276AE-C977-704C-8EA9-62202A151BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE6218E-7293-BD47-81E3-4C0F6E8CFADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30220" windowHeight="17500" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="894">
   <si>
     <t>Avatar</t>
   </si>
@@ -2687,9 +2687,6 @@
     <t>Flight Risk</t>
   </si>
   <si>
-    <t>Back to Black</t>
-  </si>
-  <si>
     <t>Dog Man</t>
   </si>
   <si>
@@ -2709,6 +2706,18 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>The Holiday</t>
+  </si>
+  <si>
+    <t>The Boy in the Striped Pyjamas</t>
+  </si>
+  <si>
+    <t>The Twilight Saga: Breaking Dawn – Part 1</t>
+  </si>
+  <si>
+    <t>Babygirl</t>
   </si>
 </sst>
 </file>
@@ -2838,7 +2847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2921,9 +2930,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2938,6 +2944,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3365,7 +3377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69789896-8E18-4F4E-96F8-276B9180E2A2}">
-  <dimension ref="A1:AE479"/>
+  <dimension ref="A1:AE484"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -3384,7 +3396,7 @@
     <col min="14" max="14" width="29.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2.6640625" style="8" customWidth="1"/>
-    <col min="17" max="17" width="17.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.83203125" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="2.6640625" style="8" customWidth="1"/>
     <col min="20" max="20" width="59.5" style="8" bestFit="1" customWidth="1"/>
@@ -3413,7 +3425,7 @@
         <v>743</v>
       </c>
       <c r="D1" s="9"/>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="31" t="s">
         <v>673</v>
       </c>
       <c r="F1" s="26" t="s">
@@ -3434,18 +3446,18 @@
         <v>415</v>
       </c>
       <c r="M1" s="9"/>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>676</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="29" t="s">
         <v>416</v>
       </c>
       <c r="P1" s="9"/>
       <c r="Q1" s="27" t="s">
+        <v>887</v>
+      </c>
+      <c r="R1" s="26" t="s">
         <v>888</v>
-      </c>
-      <c r="R1" s="26" t="s">
-        <v>889</v>
       </c>
       <c r="S1" s="9"/>
       <c r="T1" s="19" t="s">
@@ -3469,10 +3481,10 @@
         <v>854</v>
       </c>
       <c r="AB1" s="12"/>
-      <c r="AC1" s="33" t="s">
+      <c r="AC1" s="32" t="s">
         <v>877</v>
       </c>
-      <c r="AD1" s="33" t="s">
+      <c r="AD1" s="32" t="s">
         <v>878</v>
       </c>
       <c r="AE1" s="12"/>
@@ -3487,14 +3499,14 @@
       <c r="C2" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2012</v>
-      </c>
-      <c r="G2" s="10"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="34" t="s">
+        <v>816</v>
+      </c>
+      <c r="F2" s="33">
+        <v>2024</v>
+      </c>
+      <c r="G2" s="9"/>
       <c r="H2" s="3" t="s">
         <v>411</v>
       </c>
@@ -3516,8 +3528,12 @@
         <v>2019</v>
       </c>
       <c r="P2" s="10"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
+      <c r="Q2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="33">
+        <v>2023</v>
+      </c>
       <c r="S2" s="10"/>
       <c r="T2" s="21" t="s">
         <v>357</v>
@@ -3558,14 +3574,14 @@
       <c r="C3" s="17" t="s">
         <v>680</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2024</v>
-      </c>
-      <c r="G3" s="10"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="34" t="s">
+        <v>892</v>
+      </c>
+      <c r="F3" s="33">
+        <v>2011</v>
+      </c>
+      <c r="G3" s="9"/>
       <c r="H3" s="3" t="s">
         <v>41</v>
       </c>
@@ -3612,7 +3628,7 @@
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AD3" s="4">
         <v>2025</v>
@@ -3629,14 +3645,14 @@
       <c r="C4" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2004</v>
-      </c>
-      <c r="G4" s="10"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="F4" s="33">
+        <v>1986</v>
+      </c>
+      <c r="G4" s="9"/>
       <c r="H4" s="3" t="s">
         <v>95</v>
       </c>
@@ -3700,14 +3716,14 @@
       <c r="C5" s="17" t="s">
         <v>679</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1999</v>
-      </c>
-      <c r="G5" s="10"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="34" t="s">
+        <v>891</v>
+      </c>
+      <c r="F5" s="33">
+        <v>2008</v>
+      </c>
+      <c r="G5" s="9"/>
       <c r="H5" s="3" t="s">
         <v>51</v>
       </c>
@@ -3771,14 +3787,14 @@
       <c r="C6" s="17" t="s">
         <v>681</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2014</v>
-      </c>
-      <c r="G6" s="10"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="34" t="s">
+        <v>890</v>
+      </c>
+      <c r="F6" s="33">
+        <v>2006</v>
+      </c>
+      <c r="G6" s="9"/>
       <c r="H6" s="3" t="s">
         <v>410</v>
       </c>
@@ -3844,10 +3860,10 @@
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="3" t="s">
-        <v>783</v>
+        <v>94</v>
       </c>
       <c r="F7" s="2">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="3" t="s">
@@ -3894,7 +3910,7 @@
       </c>
       <c r="AB7" s="11"/>
       <c r="AC7" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AD7" s="4">
         <v>2025</v>
@@ -3913,7 +3929,7 @@
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="F8" s="2">
         <v>2024</v>
@@ -3962,8 +3978,8 @@
         <v>2024</v>
       </c>
       <c r="AB8" s="11"/>
-      <c r="AC8" s="31"/>
-      <c r="AD8" s="31"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="30"/>
       <c r="AE8" s="11"/>
     </row>
     <row r="9" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -3978,10 +3994,10 @@
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="3" t="s">
-        <v>786</v>
+        <v>803</v>
       </c>
       <c r="F9" s="2">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="3" t="s">
@@ -4040,10 +4056,10 @@
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F10" s="2">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="3" t="s">
@@ -4102,10 +4118,10 @@
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="3" t="s">
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="F11" s="2">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="3" t="s">
@@ -4164,10 +4180,10 @@
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="3" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="F12" s="2">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="3" t="s">
@@ -4226,10 +4242,10 @@
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="3" t="s">
-        <v>802</v>
+        <v>838</v>
       </c>
       <c r="F13" s="2">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="3" t="s">
@@ -4288,10 +4304,10 @@
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="3" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="F14" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="3" t="s">
@@ -4350,10 +4366,10 @@
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="3" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="F15" s="2">
-        <v>2000</v>
+        <v>2007</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="3" t="s">
@@ -4412,10 +4428,10 @@
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="3" t="s">
-        <v>563</v>
+        <v>788</v>
       </c>
       <c r="F16" s="2">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="3" t="s">
@@ -4432,8 +4448,8 @@
         <v>1994</v>
       </c>
       <c r="M16" s="10"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
       <c r="P16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="21" t="s">
@@ -4470,7 +4486,7 @@
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F17" s="2">
         <v>2011</v>
@@ -4525,10 +4541,10 @@
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="3" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="F18" s="2">
-        <v>2019</v>
+        <v>2002</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="3" t="s">
@@ -4580,10 +4596,10 @@
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="3" t="s">
-        <v>647</v>
+        <v>796</v>
       </c>
       <c r="F19" s="2">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="3" t="s">
@@ -4635,10 +4651,10 @@
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="3" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="F20" s="2">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="3" t="s">
@@ -4690,10 +4706,10 @@
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="3" t="s">
-        <v>805</v>
+        <v>563</v>
       </c>
       <c r="F21" s="2">
-        <v>2001</v>
+        <v>2019</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="3" t="s">
@@ -4745,10 +4761,10 @@
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="3" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="F22" s="2">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="3" t="s">
@@ -4800,10 +4816,10 @@
       </c>
       <c r="D23" s="10"/>
       <c r="E23" s="3" t="s">
-        <v>776</v>
+        <v>810</v>
       </c>
       <c r="F23" s="2">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="3" t="s">
@@ -4855,10 +4871,10 @@
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="3" t="s">
-        <v>435</v>
+        <v>647</v>
       </c>
       <c r="F24" s="2">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="3" t="s">
@@ -4908,12 +4924,12 @@
       <c r="C25" s="17" t="s">
         <v>697</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="3" t="s">
-        <v>836</v>
+        <v>798</v>
       </c>
       <c r="F25" s="2">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="3" t="s">
@@ -4965,10 +4981,10 @@
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="3" t="s">
-        <v>781</v>
+        <v>805</v>
       </c>
       <c r="F26" s="2">
-        <v>1990</v>
+        <v>2001</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="3" t="s">
@@ -5020,10 +5036,10 @@
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="3" t="s">
-        <v>774</v>
+        <v>784</v>
       </c>
       <c r="F27" s="2">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="3" t="s">
@@ -5075,10 +5091,10 @@
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="3" t="s">
-        <v>793</v>
+        <v>776</v>
       </c>
       <c r="F28" s="2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="3" t="s">
@@ -5130,10 +5146,10 @@
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="3" t="s">
-        <v>782</v>
+        <v>435</v>
       </c>
       <c r="F29" s="2">
-        <v>2014</v>
+        <v>1979</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="3" t="s">
@@ -5183,12 +5199,12 @@
       <c r="C30" s="17" t="s">
         <v>703</v>
       </c>
-      <c r="D30" s="10"/>
+      <c r="D30" s="11"/>
       <c r="E30" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F30" s="2">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="3" t="s">
@@ -5240,10 +5256,10 @@
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="3" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="F31" s="2">
-        <v>2022</v>
+        <v>1990</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="3" t="s">
@@ -5295,10 +5311,10 @@
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="3" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="F32" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="3" t="s">
@@ -5350,10 +5366,10 @@
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="3" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="F33" s="2">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="3" t="s">
@@ -5405,7 +5421,7 @@
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="3" t="s">
-        <v>63</v>
+        <v>782</v>
       </c>
       <c r="F34" s="2">
         <v>2014</v>
@@ -5460,10 +5476,10 @@
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="3" t="s">
-        <v>809</v>
+        <v>835</v>
       </c>
       <c r="F35" s="2">
-        <v>2023</v>
+        <v>1989</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="3" t="s">
@@ -5515,10 +5531,10 @@
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="3" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F36" s="2">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="3" t="s">
@@ -5570,10 +5586,10 @@
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="3" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="F37" s="2">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="3" t="s">
@@ -5625,10 +5641,10 @@
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="3" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
       <c r="F38" s="2">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G38" s="10"/>
       <c r="H38" s="3" t="s">
@@ -5680,10 +5696,10 @@
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="3" t="s">
-        <v>777</v>
+        <v>63</v>
       </c>
       <c r="F39" s="2">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="G39" s="10"/>
       <c r="H39" s="3" t="s">
@@ -5735,10 +5751,10 @@
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="3" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="F40" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G40" s="10"/>
       <c r="H40" s="3" t="s">
@@ -5790,10 +5806,10 @@
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="3" t="s">
-        <v>477</v>
+        <v>792</v>
       </c>
       <c r="F41" s="2">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="G41" s="10"/>
       <c r="H41" s="3" t="s">
@@ -5845,10 +5861,10 @@
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="3" t="s">
-        <v>806</v>
+        <v>773</v>
       </c>
       <c r="F42" s="2">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="G42" s="10"/>
       <c r="H42" s="3" t="s">
@@ -5900,10 +5916,10 @@
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="3" t="s">
-        <v>801</v>
+        <v>769</v>
       </c>
       <c r="F43" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G43" s="10"/>
       <c r="H43" s="3" t="s">
@@ -5955,10 +5971,10 @@
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="3" t="s">
-        <v>527</v>
+        <v>777</v>
       </c>
       <c r="F44" s="2">
-        <v>1976</v>
+        <v>2020</v>
       </c>
       <c r="G44" s="10"/>
       <c r="H44" s="3" t="s">
@@ -6010,10 +6026,10 @@
       </c>
       <c r="D45" s="10"/>
       <c r="E45" s="3" t="s">
-        <v>785</v>
+        <v>830</v>
       </c>
       <c r="F45" s="2">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="G45" s="10"/>
       <c r="H45" s="3" t="s">
@@ -6065,10 +6081,10 @@
       </c>
       <c r="D46" s="10"/>
       <c r="E46" s="3" t="s">
-        <v>789</v>
+        <v>477</v>
       </c>
       <c r="F46" s="2">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="G46" s="10"/>
       <c r="H46" s="3" t="s">
@@ -6120,10 +6136,10 @@
       </c>
       <c r="D47" s="10"/>
       <c r="E47" s="3" t="s">
-        <v>772</v>
+        <v>806</v>
       </c>
       <c r="F47" s="2">
-        <v>2023</v>
+        <v>2004</v>
       </c>
       <c r="G47" s="10"/>
       <c r="H47" s="3" t="s">
@@ -6175,10 +6191,10 @@
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="3" t="s">
-        <v>540</v>
+        <v>801</v>
       </c>
       <c r="F48" s="2">
-        <v>1986</v>
+        <v>2018</v>
       </c>
       <c r="G48" s="10"/>
       <c r="H48" s="3" t="s">
@@ -6230,10 +6246,10 @@
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="3" t="s">
-        <v>787</v>
+        <v>527</v>
       </c>
       <c r="F49" s="2">
-        <v>2021</v>
+        <v>1976</v>
       </c>
       <c r="G49" s="10"/>
       <c r="H49" s="3" t="s">
@@ -6285,10 +6301,10 @@
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="3" t="s">
-        <v>13</v>
+        <v>785</v>
       </c>
       <c r="F50" s="2">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G50" s="10"/>
       <c r="H50" s="3" t="s">
@@ -6340,10 +6356,10 @@
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="3" t="s">
-        <v>780</v>
+        <v>789</v>
       </c>
       <c r="F51" s="2">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="G51" s="10"/>
       <c r="H51" s="3" t="s">
@@ -6376,7 +6392,7 @@
       </c>
       <c r="Y51" s="11"/>
       <c r="Z51" s="18" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="AA51" s="18">
         <v>2024</v>
@@ -6395,10 +6411,10 @@
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="F52" s="2">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="G52" s="10"/>
       <c r="H52" s="3" t="s">
@@ -6446,10 +6462,10 @@
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="3" t="s">
-        <v>778</v>
+        <v>540</v>
       </c>
       <c r="F53" s="2">
-        <v>2006</v>
+        <v>1986</v>
       </c>
       <c r="G53" s="10"/>
       <c r="H53" s="3" t="s">
@@ -6495,10 +6511,10 @@
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="3" t="s">
-        <v>418</v>
+        <v>787</v>
       </c>
       <c r="F54" s="2">
-        <v>1975</v>
+        <v>2021</v>
       </c>
       <c r="G54" s="10"/>
       <c r="H54" s="3" t="s">
@@ -6544,10 +6560,10 @@
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="3" t="s">
-        <v>768</v>
+        <v>13</v>
       </c>
       <c r="F55" s="2">
-        <v>1984</v>
+        <v>2019</v>
       </c>
       <c r="G55" s="10"/>
       <c r="H55" s="3" t="s">
@@ -6593,10 +6609,10 @@
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="3" t="s">
-        <v>538</v>
+        <v>780</v>
       </c>
       <c r="F56" s="2">
-        <v>1939</v>
+        <v>1999</v>
       </c>
       <c r="G56" s="10"/>
       <c r="H56" s="3" t="s">
@@ -6642,10 +6658,10 @@
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="3" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="F57" s="2">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="G57" s="10"/>
       <c r="H57" s="3" t="s">
@@ -6691,10 +6707,10 @@
       </c>
       <c r="D58" s="10"/>
       <c r="E58" s="3" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="F58" s="2">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="G58" s="10"/>
       <c r="H58" s="3" t="s">
@@ -6740,10 +6756,10 @@
       </c>
       <c r="D59" s="10"/>
       <c r="E59" s="3" t="s">
-        <v>762</v>
+        <v>418</v>
       </c>
       <c r="F59" s="2">
-        <v>2008</v>
+        <v>1975</v>
       </c>
       <c r="G59" s="10"/>
       <c r="H59" s="3" t="s">
@@ -6789,10 +6805,10 @@
       </c>
       <c r="D60" s="10"/>
       <c r="E60" s="3" t="s">
-        <v>669</v>
+        <v>768</v>
       </c>
       <c r="F60" s="2">
-        <v>2023</v>
+        <v>1984</v>
       </c>
       <c r="G60" s="10"/>
       <c r="H60" s="3" t="s">
@@ -6838,10 +6854,10 @@
       </c>
       <c r="D61" s="10"/>
       <c r="E61" s="3" t="s">
-        <v>826</v>
+        <v>538</v>
       </c>
       <c r="F61" s="2">
-        <v>2024</v>
+        <v>1939</v>
       </c>
       <c r="G61" s="10"/>
       <c r="H61" s="3" t="s">
@@ -6887,10 +6903,10 @@
       </c>
       <c r="D62" s="10"/>
       <c r="E62" s="3" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="F62" s="2">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="G62" s="10"/>
       <c r="H62" s="3" t="s">
@@ -6936,10 +6952,10 @@
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="3" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="F63" s="2">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="3" t="s">
@@ -6985,10 +7001,10 @@
       </c>
       <c r="D64" s="10"/>
       <c r="E64" s="3" t="s">
-        <v>463</v>
+        <v>762</v>
       </c>
       <c r="F64" s="2">
-        <v>1987</v>
+        <v>2008</v>
       </c>
       <c r="G64" s="10"/>
       <c r="H64" s="3" t="s">
@@ -7034,10 +7050,10 @@
       </c>
       <c r="D65" s="10"/>
       <c r="E65" s="3" t="s">
-        <v>55</v>
+        <v>669</v>
       </c>
       <c r="F65" s="2">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G65" s="10"/>
       <c r="H65" s="3" t="s">
@@ -7047,8 +7063,12 @@
         <v>2003</v>
       </c>
       <c r="J65" s="10"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
+      <c r="K65" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="L65" s="2">
+        <v>1985</v>
+      </c>
       <c r="M65" s="11"/>
       <c r="S65" s="11"/>
       <c r="T65" s="21" t="s">
@@ -7079,10 +7099,10 @@
       </c>
       <c r="D66" s="10"/>
       <c r="E66" s="3" t="s">
-        <v>797</v>
+        <v>826</v>
       </c>
       <c r="F66" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="G66" s="10"/>
       <c r="H66" s="3" t="s">
@@ -7092,6 +7112,9 @@
         <v>1994</v>
       </c>
       <c r="J66" s="10"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="11"/>
       <c r="S66" s="11"/>
       <c r="T66" s="21" t="s">
         <v>440</v>
@@ -7121,10 +7144,10 @@
       </c>
       <c r="D67" s="10"/>
       <c r="E67" s="3" t="s">
-        <v>22</v>
+        <v>767</v>
       </c>
       <c r="F67" s="2">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="G67" s="10"/>
       <c r="H67" s="3" t="s">
@@ -7163,10 +7186,10 @@
       </c>
       <c r="D68" s="10"/>
       <c r="E68" s="3" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="F68" s="2">
-        <v>2009</v>
+        <v>2000</v>
       </c>
       <c r="G68" s="10"/>
       <c r="H68" s="3" t="s">
@@ -7205,10 +7228,10 @@
       </c>
       <c r="D69" s="10"/>
       <c r="E69" s="3" t="s">
-        <v>766</v>
+        <v>463</v>
       </c>
       <c r="F69" s="2">
-        <v>2011</v>
+        <v>1987</v>
       </c>
       <c r="G69" s="10"/>
       <c r="H69" s="3" t="s">
@@ -7247,10 +7270,10 @@
       </c>
       <c r="D70" s="10"/>
       <c r="E70" s="3" t="s">
-        <v>763</v>
+        <v>55</v>
       </c>
       <c r="F70" s="2">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="G70" s="10"/>
       <c r="H70" s="3" t="s">
@@ -7289,10 +7312,10 @@
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="3" t="s">
-        <v>760</v>
+        <v>797</v>
       </c>
       <c r="F71" s="2">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="G71" s="10"/>
       <c r="H71" s="3" t="s">
@@ -7331,10 +7354,10 @@
       </c>
       <c r="D72" s="10"/>
       <c r="E72" s="3" t="s">
-        <v>771</v>
+        <v>22</v>
       </c>
       <c r="F72" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G72" s="10"/>
       <c r="H72" s="3" t="s">
@@ -7371,12 +7394,12 @@
       <c r="C73" s="17" t="s">
         <v>694</v>
       </c>
-      <c r="D73" s="11"/>
+      <c r="D73" s="10"/>
       <c r="E73" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="F73" s="2">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="G73" s="10"/>
       <c r="H73" s="3" t="s">
@@ -7415,10 +7438,10 @@
       </c>
       <c r="D74" s="10"/>
       <c r="E74" s="3" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="F74" s="2">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="G74" s="10"/>
       <c r="H74" s="3" t="s">
@@ -7447,20 +7470,20 @@
     </row>
     <row r="75" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B75" s="17">
         <v>2025</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D75" s="10"/>
       <c r="E75" s="3" t="s">
-        <v>825</v>
+        <v>763</v>
       </c>
       <c r="F75" s="2">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="G75" s="10"/>
       <c r="H75" s="3" t="s">
@@ -7499,10 +7522,10 @@
       </c>
       <c r="D76" s="10"/>
       <c r="E76" s="3" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="F76" s="2">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="G76" s="10"/>
       <c r="H76" s="3" t="s">
@@ -7541,10 +7564,10 @@
       </c>
       <c r="D77" s="10"/>
       <c r="E77" s="3" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="F77" s="2">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="G77" s="10"/>
       <c r="H77" s="3" t="s">
@@ -7581,12 +7604,12 @@
       <c r="C78" s="17" t="s">
         <v>705</v>
       </c>
-      <c r="D78" s="10"/>
+      <c r="D78" s="11"/>
       <c r="E78" s="3" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="F78" s="2">
-        <v>1999</v>
+        <v>2006</v>
       </c>
       <c r="G78" s="10"/>
       <c r="H78" s="3" t="s">
@@ -7625,7 +7648,7 @@
       </c>
       <c r="D79" s="10"/>
       <c r="E79" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F79" s="2">
         <v>2018</v>
@@ -7667,10 +7690,10 @@
       </c>
       <c r="D80" s="10"/>
       <c r="E80" s="3" t="s">
-        <v>30</v>
+        <v>825</v>
       </c>
       <c r="F80" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G80" s="10"/>
       <c r="H80" s="3" t="s">
@@ -7709,10 +7732,10 @@
       </c>
       <c r="D81" s="10"/>
       <c r="E81" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F81" s="2">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="G81" s="10"/>
       <c r="H81" s="3" t="s">
@@ -7751,10 +7774,10 @@
       </c>
       <c r="D82" s="10"/>
       <c r="E82" s="3" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="F82" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="G82" s="10"/>
       <c r="H82" s="3" t="s">
@@ -7793,10 +7816,10 @@
       </c>
       <c r="D83" s="10"/>
       <c r="E83" s="3" t="s">
-        <v>808</v>
+        <v>765</v>
       </c>
       <c r="F83" s="2">
-        <v>2024</v>
+        <v>1999</v>
       </c>
       <c r="G83" s="10"/>
       <c r="H83" s="3" t="s">
@@ -7835,7 +7858,7 @@
       </c>
       <c r="D84" s="10"/>
       <c r="E84" s="3" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="F84" s="2">
         <v>2018</v>
@@ -7877,10 +7900,10 @@
       </c>
       <c r="D85" s="10"/>
       <c r="E85" s="3" t="s">
-        <v>752</v>
+        <v>30</v>
       </c>
       <c r="F85" s="2">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="G85" s="10"/>
       <c r="H85" s="3" t="s">
@@ -7919,10 +7942,10 @@
       </c>
       <c r="D86" s="10"/>
       <c r="E86" s="3" t="s">
-        <v>819</v>
+        <v>754</v>
       </c>
       <c r="F86" s="2">
-        <v>1991</v>
+        <v>2018</v>
       </c>
       <c r="G86" s="10"/>
       <c r="H86" s="3" t="s">
@@ -7961,10 +7984,10 @@
       </c>
       <c r="D87" s="10"/>
       <c r="E87" s="3" t="s">
-        <v>486</v>
+        <v>750</v>
       </c>
       <c r="F87" s="2">
-        <v>1982</v>
+        <v>2021</v>
       </c>
       <c r="G87" s="10"/>
       <c r="H87" s="3" t="s">
@@ -8003,10 +8026,10 @@
       </c>
       <c r="D88" s="10"/>
       <c r="E88" s="3" t="s">
-        <v>749</v>
+        <v>808</v>
       </c>
       <c r="F88" s="2">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="G88" s="10"/>
       <c r="H88" s="3" t="s">
@@ -8045,10 +8068,10 @@
       </c>
       <c r="D89" s="10"/>
       <c r="E89" s="3" t="s">
-        <v>824</v>
+        <v>751</v>
       </c>
       <c r="F89" s="2">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="G89" s="10"/>
       <c r="H89" s="3" t="s">
@@ -8087,10 +8110,10 @@
       </c>
       <c r="D90" s="10"/>
       <c r="E90" s="3" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="F90" s="2">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="G90" s="10"/>
       <c r="H90" s="3" t="s">
@@ -8129,10 +8152,10 @@
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="3" t="s">
-        <v>59</v>
+        <v>819</v>
       </c>
       <c r="F91" s="2">
-        <v>2013</v>
+        <v>1991</v>
       </c>
       <c r="G91" s="10"/>
       <c r="H91" s="3" t="s">
@@ -8171,10 +8194,10 @@
       </c>
       <c r="D92" s="10"/>
       <c r="E92" s="3" t="s">
-        <v>99</v>
+        <v>486</v>
       </c>
       <c r="F92" s="2">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="G92" s="10"/>
       <c r="H92" s="3" t="s">
@@ -8213,10 +8236,10 @@
       </c>
       <c r="D93" s="10"/>
       <c r="E93" s="3" t="s">
-        <v>100</v>
+        <v>749</v>
       </c>
       <c r="F93" s="2">
-        <v>1989</v>
+        <v>2014</v>
       </c>
       <c r="G93" s="10"/>
       <c r="H93" s="3" t="s">
@@ -8255,10 +8278,10 @@
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="3" t="s">
-        <v>101</v>
+        <v>824</v>
       </c>
       <c r="F94" s="2">
-        <v>1989</v>
+        <v>2022</v>
       </c>
       <c r="G94" s="10"/>
       <c r="H94" s="3" t="s">
@@ -8297,10 +8320,10 @@
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="3" t="s">
-        <v>102</v>
+        <v>744</v>
       </c>
       <c r="F95" s="2">
-        <v>2015</v>
+        <v>2003</v>
       </c>
       <c r="G95" s="10"/>
       <c r="H95" s="3" t="s">
@@ -8339,10 +8362,10 @@
       </c>
       <c r="D96" s="10"/>
       <c r="E96" s="3" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F96" s="2">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="G96" s="10"/>
       <c r="H96" s="3" t="s">
@@ -8381,10 +8404,10 @@
       </c>
       <c r="D97" s="10"/>
       <c r="E97" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F97" s="2">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="G97" s="10"/>
       <c r="H97" s="3" t="s">
@@ -8423,10 +8446,10 @@
       </c>
       <c r="D98" s="10"/>
       <c r="E98" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F98" s="2">
-        <v>1957</v>
+        <v>1989</v>
       </c>
       <c r="G98" s="10"/>
       <c r="H98" s="3" t="s">
@@ -8465,10 +8488,10 @@
       </c>
       <c r="D99" s="10"/>
       <c r="E99" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F99" s="2">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="G99" s="10"/>
       <c r="H99" s="3" t="s">
@@ -8507,10 +8530,10 @@
       </c>
       <c r="D100" s="10"/>
       <c r="E100" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F100" s="2">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="G100" s="10"/>
       <c r="H100" s="3" t="s">
@@ -8549,10 +8572,10 @@
       </c>
       <c r="D101" s="10"/>
       <c r="E101" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F101" s="2">
-        <v>2013</v>
+        <v>2007</v>
       </c>
       <c r="G101" s="10"/>
       <c r="H101" s="3" t="s">
@@ -8583,12 +8606,12 @@
       <c r="A102" s="11"/>
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
+      <c r="D102" s="10"/>
       <c r="E102" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F102" s="2">
-        <v>2011</v>
+        <v>1990</v>
       </c>
       <c r="G102" s="10"/>
       <c r="H102" s="3" t="s">
@@ -8616,12 +8639,12 @@
       <c r="AA102" s="7"/>
     </row>
     <row r="103" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D103" s="11"/>
+      <c r="D103" s="10"/>
       <c r="E103" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F103" s="2">
-        <v>1999</v>
+        <v>1957</v>
       </c>
       <c r="G103" s="10"/>
       <c r="H103" s="3" t="s">
@@ -8649,12 +8672,12 @@
       <c r="AA103" s="7"/>
     </row>
     <row r="104" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D104" s="11"/>
+      <c r="D104" s="10"/>
       <c r="E104" s="3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="F104" s="2">
-        <v>2024</v>
+        <v>1993</v>
       </c>
       <c r="G104" s="10"/>
       <c r="H104" s="3" t="s">
@@ -8682,9 +8705,9 @@
       <c r="AA104" s="7"/>
     </row>
     <row r="105" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D105" s="11"/>
+      <c r="D105" s="10"/>
       <c r="E105" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F105" s="2">
         <v>2009</v>
@@ -8715,12 +8738,12 @@
       <c r="AA105" s="7"/>
     </row>
     <row r="106" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D106" s="11"/>
+      <c r="D106" s="10"/>
       <c r="E106" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F106" s="2">
-        <v>1994</v>
+        <v>2013</v>
       </c>
       <c r="G106" s="10"/>
       <c r="H106" s="3" t="s">
@@ -8750,7 +8773,7 @@
     <row r="107" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="11"/>
       <c r="E107" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F107" s="2">
         <v>2011</v>
@@ -8783,10 +8806,10 @@
     <row r="108" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="11"/>
       <c r="E108" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F108" s="2">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="G108" s="10"/>
       <c r="H108" s="3" t="s">
@@ -8815,14 +8838,14 @@
     </row>
     <row r="109" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D109" s="11"/>
       <c r="E109" s="3" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="F109" s="2">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="G109" s="10"/>
       <c r="H109" s="3" t="s">
@@ -8852,10 +8875,10 @@
     <row r="110" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="11"/>
       <c r="E110" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F110" s="2">
-        <v>1973</v>
+        <v>2009</v>
       </c>
       <c r="G110" s="10"/>
       <c r="H110" s="3" t="s">
@@ -8885,10 +8908,10 @@
     <row r="111" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="11"/>
       <c r="E111" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F111" s="2">
-        <v>2004</v>
+        <v>1994</v>
       </c>
       <c r="G111" s="10"/>
       <c r="H111" s="3" t="s">
@@ -8918,10 +8941,10 @@
     <row r="112" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D112" s="11"/>
       <c r="E112" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F112" s="2">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="G112" s="10"/>
       <c r="H112" s="3" t="s">
@@ -8951,10 +8974,10 @@
     <row r="113" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D113" s="11"/>
       <c r="E113" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F113" s="2">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="G113" s="10"/>
       <c r="H113" s="3" t="s">
@@ -8984,10 +9007,10 @@
     <row r="114" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D114" s="11"/>
       <c r="E114" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F114" s="2">
-        <v>1984</v>
+        <v>2013</v>
       </c>
       <c r="G114" s="10"/>
       <c r="H114" s="3" t="s">
@@ -9017,10 +9040,10 @@
     <row r="115" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D115" s="11"/>
       <c r="E115" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F115" s="2">
-        <v>2008</v>
+        <v>1973</v>
       </c>
       <c r="G115" s="10"/>
       <c r="H115" s="3" t="s">
@@ -9050,10 +9073,10 @@
     <row r="116" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D116" s="11"/>
       <c r="E116" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F116" s="2">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="G116" s="10"/>
       <c r="H116" s="3" t="s">
@@ -9083,10 +9106,10 @@
     <row r="117" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D117" s="11"/>
       <c r="E117" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F117" s="2">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="G117" s="10"/>
       <c r="H117" s="3" t="s">
@@ -9116,10 +9139,10 @@
     <row r="118" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="11"/>
       <c r="E118" s="3" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="F118" s="2">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="G118" s="10"/>
       <c r="H118" s="3" t="s">
@@ -9149,10 +9172,10 @@
     <row r="119" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="11"/>
       <c r="E119" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F119" s="2">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="G119" s="10"/>
       <c r="H119" s="3" t="s">
@@ -9182,10 +9205,10 @@
     <row r="120" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D120" s="11"/>
       <c r="E120" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F120" s="2">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="G120" s="10"/>
       <c r="H120" s="3" t="s">
@@ -9215,10 +9238,10 @@
     <row r="121" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D121" s="11"/>
       <c r="E121" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F121" s="2">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="G121" s="10"/>
       <c r="H121" s="3" t="s">
@@ -9248,10 +9271,10 @@
     <row r="122" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D122" s="11"/>
       <c r="E122" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F122" s="2">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G122" s="10"/>
       <c r="H122" s="3" t="s">
@@ -9281,10 +9304,10 @@
     <row r="123" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D123" s="11"/>
       <c r="E123" s="3" t="s">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="F123" s="2">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="G123" s="10"/>
       <c r="H123" s="3" t="s">
@@ -9314,10 +9337,10 @@
     <row r="124" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D124" s="11"/>
       <c r="E124" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F124" s="2">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="G124" s="10"/>
       <c r="H124" s="3" t="s">
@@ -9347,10 +9370,10 @@
     <row r="125" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D125" s="11"/>
       <c r="E125" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F125" s="2">
-        <v>1995</v>
+        <v>2023</v>
       </c>
       <c r="G125" s="10"/>
       <c r="H125" s="3" t="s">
@@ -9380,10 +9403,10 @@
     <row r="126" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D126" s="11"/>
       <c r="E126" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F126" s="2">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="G126" s="10"/>
       <c r="H126" s="3" t="s">
@@ -9413,10 +9436,10 @@
     <row r="127" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D127" s="11"/>
       <c r="E127" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F127" s="2">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="G127" s="10"/>
       <c r="H127" s="4" t="s">
@@ -9446,10 +9469,10 @@
     <row r="128" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D128" s="11"/>
       <c r="E128" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F128" s="2">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="G128" s="10"/>
       <c r="H128" s="4" t="s">
@@ -9479,10 +9502,10 @@
     <row r="129" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D129" s="11"/>
       <c r="E129" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F129" s="2">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="G129" s="10"/>
       <c r="H129" s="4" t="s">
@@ -9512,10 +9535,10 @@
     <row r="130" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D130" s="11"/>
       <c r="E130" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F130" s="2">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="G130" s="10"/>
       <c r="H130" s="4" t="s">
@@ -9545,10 +9568,10 @@
     <row r="131" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D131" s="11"/>
       <c r="E131" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F131" s="2">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="G131" s="10"/>
       <c r="H131" s="4" t="s">
@@ -9578,10 +9601,10 @@
     <row r="132" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D132" s="11"/>
       <c r="E132" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F132" s="2">
-        <v>1986</v>
+        <v>2007</v>
       </c>
       <c r="G132" s="10"/>
       <c r="H132" s="4" t="s">
@@ -9611,10 +9634,10 @@
     <row r="133" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D133" s="11"/>
       <c r="E133" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F133" s="2">
-        <v>2005</v>
+        <v>1995</v>
       </c>
       <c r="G133" s="10"/>
       <c r="H133" s="4" t="s">
@@ -9644,10 +9667,10 @@
     <row r="134" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D134" s="11"/>
       <c r="E134" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F134" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="G134" s="10"/>
       <c r="H134" s="4" t="s">
@@ -9677,10 +9700,10 @@
     <row r="135" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D135" s="11"/>
       <c r="E135" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F135" s="2">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="G135" s="10"/>
       <c r="H135" s="4" t="s">
@@ -9710,10 +9733,10 @@
     <row r="136" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D136" s="11"/>
       <c r="E136" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F136" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="G136" s="10"/>
       <c r="H136" s="4" t="s">
@@ -9743,10 +9766,10 @@
     <row r="137" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D137" s="11"/>
       <c r="E137" s="3" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="F137" s="2">
-        <v>2016</v>
+        <v>1986</v>
       </c>
       <c r="G137" s="10"/>
       <c r="H137" s="4" t="s">
@@ -9776,7 +9799,7 @@
     <row r="138" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="11"/>
       <c r="E138" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F138" s="2">
         <v>2005</v>
@@ -9809,10 +9832,10 @@
     <row r="139" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D139" s="11"/>
       <c r="E139" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F139" s="2">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G139" s="10"/>
       <c r="H139" s="4" t="s">
@@ -9842,10 +9865,10 @@
     <row r="140" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D140" s="11"/>
       <c r="E140" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F140" s="2">
-        <v>2023</v>
+        <v>1997</v>
       </c>
       <c r="G140" s="10"/>
       <c r="H140" s="4" t="s">
@@ -9875,10 +9898,10 @@
     <row r="141" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D141" s="11"/>
       <c r="E141" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F141" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G141" s="10"/>
       <c r="H141" s="4" t="s">
@@ -9908,10 +9931,10 @@
     <row r="142" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D142" s="11"/>
       <c r="E142" s="3" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="F142" s="2">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="G142" s="10"/>
       <c r="H142" s="4" t="s">
@@ -9941,10 +9964,10 @@
     <row r="143" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D143" s="11"/>
       <c r="E143" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F143" s="2">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="G143" s="10"/>
       <c r="H143" s="4" t="s">
@@ -9974,10 +9997,10 @@
     <row r="144" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D144" s="11"/>
       <c r="E144" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F144" s="2">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="G144" s="10"/>
       <c r="H144" s="4" t="s">
@@ -10007,10 +10030,10 @@
     <row r="145" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D145" s="11"/>
       <c r="E145" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F145" s="2">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G145" s="10"/>
       <c r="H145" s="4" t="s">
@@ -10040,10 +10063,10 @@
     <row r="146" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D146" s="11"/>
       <c r="E146" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F146" s="2">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="G146" s="10"/>
       <c r="H146" s="4" t="s">
@@ -10073,10 +10096,10 @@
     <row r="147" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D147" s="11"/>
       <c r="E147" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F147" s="2">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="G147" s="10"/>
       <c r="H147" s="4" t="s">
@@ -10106,10 +10129,10 @@
     <row r="148" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D148" s="11"/>
       <c r="E148" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F148" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G148" s="10"/>
       <c r="H148" s="4" t="s">
@@ -10139,10 +10162,10 @@
     <row r="149" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D149" s="11"/>
       <c r="E149" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F149" s="2">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="G149" s="10"/>
       <c r="H149" s="4" t="s">
@@ -10172,10 +10195,10 @@
     <row r="150" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D150" s="11"/>
       <c r="E150" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F150" s="2">
-        <v>1996</v>
+        <v>2013</v>
       </c>
       <c r="G150" s="10"/>
       <c r="H150" s="4" t="s">
@@ -10205,10 +10228,10 @@
     <row r="151" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D151" s="11"/>
       <c r="E151" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F151" s="2">
-        <v>1998</v>
+        <v>2020</v>
       </c>
       <c r="G151" s="10"/>
       <c r="H151" s="4" t="s">
@@ -10238,10 +10261,10 @@
     <row r="152" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D152" s="11"/>
       <c r="E152" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F152" s="2">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="G152" s="10"/>
       <c r="H152" s="4" t="s">
@@ -10271,10 +10294,10 @@
     <row r="153" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D153" s="11"/>
       <c r="E153" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F153" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G153" s="10"/>
       <c r="H153" s="4" t="s">
@@ -10304,10 +10327,10 @@
     <row r="154" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D154" s="11"/>
       <c r="E154" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F154" s="2">
-        <v>2023</v>
+        <v>2009</v>
       </c>
       <c r="G154" s="10"/>
       <c r="H154" s="4" t="s">
@@ -10337,10 +10360,10 @@
     <row r="155" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D155" s="11"/>
       <c r="E155" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F155" s="2">
-        <v>1978</v>
+        <v>1996</v>
       </c>
       <c r="G155" s="10"/>
       <c r="H155" s="4" t="s">
@@ -10370,10 +10393,10 @@
     <row r="156" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D156" s="11"/>
       <c r="E156" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F156" s="2">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="G156" s="10"/>
       <c r="H156" s="4" t="s">
@@ -10403,10 +10426,10 @@
     <row r="157" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D157" s="11"/>
       <c r="E157" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F157" s="2">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="G157" s="10"/>
       <c r="H157" s="4" t="s">
@@ -10436,10 +10459,10 @@
     <row r="158" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D158" s="11"/>
       <c r="E158" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F158" s="2">
-        <v>1989</v>
+        <v>2022</v>
       </c>
       <c r="G158" s="10"/>
       <c r="H158" s="4" t="s">
@@ -10469,10 +10492,10 @@
     <row r="159" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D159" s="11"/>
       <c r="E159" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F159" s="2">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="G159" s="10"/>
       <c r="H159" s="4" t="s">
@@ -10502,10 +10525,10 @@
     <row r="160" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D160" s="11"/>
       <c r="E160" s="3" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="F160" s="2">
-        <v>2022</v>
+        <v>1978</v>
       </c>
       <c r="G160" s="10"/>
       <c r="H160" s="4" t="s">
@@ -10535,10 +10558,10 @@
     <row r="161" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="11"/>
       <c r="E161" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F161" s="2">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="G161" s="10"/>
       <c r="H161" s="4" t="s">
@@ -10568,10 +10591,10 @@
     <row r="162" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="11"/>
       <c r="E162" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F162" s="2">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="G162" s="10"/>
       <c r="H162" s="4" t="s">
@@ -10601,10 +10624,10 @@
     <row r="163" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="11"/>
       <c r="E163" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F163" s="2">
-        <v>2006</v>
+        <v>1989</v>
       </c>
       <c r="G163" s="10"/>
       <c r="H163" s="4" t="s">
@@ -10634,10 +10657,10 @@
     <row r="164" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="11"/>
       <c r="E164" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F164" s="2">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="G164" s="10"/>
       <c r="H164" s="4" t="s">
@@ -10667,10 +10690,10 @@
     <row r="165" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D165" s="11"/>
       <c r="E165" s="3" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
       <c r="F165" s="2">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="G165" s="10"/>
       <c r="H165" s="4" t="s">
@@ -10700,10 +10723,10 @@
     <row r="166" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D166" s="11"/>
       <c r="E166" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F166" s="2">
-        <v>1996</v>
+        <v>2024</v>
       </c>
       <c r="G166" s="10"/>
       <c r="H166" s="4" t="s">
@@ -10733,10 +10756,10 @@
     <row r="167" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="11"/>
       <c r="E167" s="3" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="F167" s="2">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="G167" s="10"/>
       <c r="H167" s="4" t="s">
@@ -10766,10 +10789,10 @@
     <row r="168" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="11"/>
       <c r="E168" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F168" s="2">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="G168" s="10"/>
       <c r="H168" s="4" t="s">
@@ -10799,10 +10822,10 @@
     <row r="169" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="11"/>
       <c r="E169" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F169" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="G169" s="10"/>
       <c r="H169" s="4" t="s">
@@ -10832,10 +10855,10 @@
     <row r="170" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="11"/>
       <c r="E170" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F170" s="2">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="G170" s="10"/>
       <c r="H170" s="4" t="s">
@@ -10865,10 +10888,10 @@
     <row r="171" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D171" s="11"/>
       <c r="E171" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F171" s="2">
-        <v>2001</v>
+        <v>1996</v>
       </c>
       <c r="G171" s="10"/>
       <c r="H171" s="4" t="s">
@@ -10898,10 +10921,10 @@
     <row r="172" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D172" s="11"/>
       <c r="E172" s="3" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="F172" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="G172" s="10"/>
       <c r="H172" s="4" t="s">
@@ -10931,10 +10954,10 @@
     <row r="173" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="11"/>
       <c r="E173" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F173" s="2">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="G173" s="10"/>
       <c r="H173" s="4" t="s">
@@ -10964,10 +10987,10 @@
     <row r="174" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="11"/>
       <c r="E174" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F174" s="2">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="G174" s="10"/>
       <c r="H174" s="4" t="s">
@@ -10997,10 +11020,10 @@
     <row r="175" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="11"/>
       <c r="E175" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F175" s="2">
-        <v>1988</v>
+        <v>2011</v>
       </c>
       <c r="G175" s="10"/>
       <c r="H175" s="4" t="s">
@@ -11030,14 +11053,14 @@
     <row r="176" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D176" s="11"/>
       <c r="E176" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F176" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="G176" s="10"/>
-      <c r="H176" s="31"/>
-      <c r="I176" s="31"/>
+      <c r="H176" s="30"/>
+      <c r="I176" s="30"/>
       <c r="J176" s="11"/>
       <c r="S176" s="11"/>
       <c r="T176" s="21" t="s">
@@ -11059,10 +11082,10 @@
     <row r="177" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D177" s="11"/>
       <c r="E177" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F177" s="2">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="G177" s="10"/>
       <c r="S177" s="11"/>
@@ -11085,10 +11108,10 @@
     <row r="178" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="11"/>
       <c r="E178" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F178" s="2">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="G178" s="10"/>
       <c r="S178" s="11"/>
@@ -11111,7 +11134,7 @@
     <row r="179" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="11"/>
       <c r="E179" s="3" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="F179" s="2">
         <v>2017</v>
@@ -11137,10 +11160,10 @@
     <row r="180" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="11"/>
       <c r="E180" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F180" s="2">
-        <v>1998</v>
+        <v>1988</v>
       </c>
       <c r="G180" s="10"/>
       <c r="S180" s="11"/>
@@ -11163,10 +11186,10 @@
     <row r="181" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="11"/>
       <c r="E181" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F181" s="2">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="G181" s="10"/>
       <c r="S181" s="11"/>
@@ -11189,10 +11212,10 @@
     <row r="182" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="11"/>
       <c r="E182" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F182" s="2">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="G182" s="10"/>
       <c r="S182" s="11"/>
@@ -11215,10 +11238,10 @@
     <row r="183" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="11"/>
       <c r="E183" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F183" s="2">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="G183" s="10"/>
       <c r="S183" s="11"/>
@@ -11241,10 +11264,10 @@
     <row r="184" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="11"/>
       <c r="E184" s="3" t="s">
-        <v>185</v>
+        <v>57</v>
       </c>
       <c r="F184" s="2">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="G184" s="10"/>
       <c r="S184" s="11"/>
@@ -11267,10 +11290,10 @@
     <row r="185" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="11"/>
       <c r="E185" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F185" s="2">
-        <v>1978</v>
+        <v>1998</v>
       </c>
       <c r="G185" s="10"/>
       <c r="S185" s="11"/>
@@ -11293,10 +11316,10 @@
     <row r="186" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="11"/>
       <c r="E186" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F186" s="2">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="G186" s="10"/>
       <c r="S186" s="11"/>
@@ -11319,10 +11342,10 @@
     <row r="187" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="11"/>
       <c r="E187" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F187" s="2">
-        <v>1974</v>
+        <v>2010</v>
       </c>
       <c r="G187" s="10"/>
       <c r="S187" s="11"/>
@@ -11345,10 +11368,10 @@
     <row r="188" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="11"/>
       <c r="E188" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F188" s="2">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="G188" s="10"/>
       <c r="S188" s="11"/>
@@ -11371,10 +11394,10 @@
     <row r="189" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="11"/>
       <c r="E189" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F189" s="2">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="G189" s="10"/>
       <c r="S189" s="11"/>
@@ -11397,10 +11420,10 @@
     <row r="190" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="11"/>
       <c r="E190" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F190" s="2">
-        <v>1992</v>
+        <v>1978</v>
       </c>
       <c r="G190" s="10"/>
       <c r="S190" s="11"/>
@@ -11423,10 +11446,10 @@
     <row r="191" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="11"/>
       <c r="E191" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F191" s="2">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="G191" s="10"/>
       <c r="S191" s="11"/>
@@ -11449,10 +11472,10 @@
     <row r="192" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="11"/>
       <c r="E192" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F192" s="2">
-        <v>2017</v>
+        <v>1974</v>
       </c>
       <c r="G192" s="10"/>
       <c r="S192" s="11"/>
@@ -11475,10 +11498,10 @@
     <row r="193" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="11"/>
       <c r="E193" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F193" s="2">
-        <v>2022</v>
+        <v>2003</v>
       </c>
       <c r="G193" s="10"/>
       <c r="S193" s="11"/>
@@ -11501,10 +11524,10 @@
     <row r="194" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="11"/>
       <c r="E194" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F194" s="2">
-        <v>2018</v>
+        <v>1983</v>
       </c>
       <c r="G194" s="10"/>
       <c r="S194" s="11"/>
@@ -11527,10 +11550,10 @@
     <row r="195" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="11"/>
       <c r="E195" s="3" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="F195" s="2">
-        <v>2023</v>
+        <v>1992</v>
       </c>
       <c r="G195" s="10"/>
       <c r="S195" s="11"/>
@@ -11553,10 +11576,10 @@
     <row r="196" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="11"/>
       <c r="E196" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F196" s="2">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="G196" s="10"/>
       <c r="S196" s="11"/>
@@ -11579,10 +11602,10 @@
     <row r="197" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="11"/>
       <c r="E197" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F197" s="2">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G197" s="10"/>
       <c r="S197" s="11"/>
@@ -11605,10 +11628,10 @@
     <row r="198" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="11"/>
       <c r="E198" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F198" s="2">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="G198" s="10"/>
       <c r="S198" s="11"/>
@@ -11631,10 +11654,10 @@
     <row r="199" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="11"/>
       <c r="E199" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F199" s="2">
-        <v>1996</v>
+        <v>2018</v>
       </c>
       <c r="G199" s="10"/>
       <c r="S199" s="11"/>
@@ -11657,10 +11680,10 @@
     <row r="200" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D200" s="11"/>
       <c r="E200" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F200" s="2">
-        <v>1991</v>
+        <v>2023</v>
       </c>
       <c r="G200" s="10"/>
       <c r="S200" s="11"/>
@@ -11683,10 +11706,10 @@
     <row r="201" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D201" s="11"/>
       <c r="E201" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F201" s="2">
-        <v>2018</v>
+        <v>1988</v>
       </c>
       <c r="G201" s="10"/>
       <c r="S201" s="11"/>
@@ -11709,10 +11732,10 @@
     <row r="202" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="11"/>
       <c r="E202" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F202" s="2">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="G202" s="10"/>
       <c r="S202" s="11"/>
@@ -11734,10 +11757,10 @@
     <row r="203" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="11"/>
       <c r="E203" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F203" s="2">
-        <v>1999</v>
+        <v>2012</v>
       </c>
       <c r="G203" s="10"/>
       <c r="S203" s="11"/>
@@ -11759,10 +11782,10 @@
     <row r="204" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="11"/>
       <c r="E204" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F204" s="2">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="G204" s="10"/>
       <c r="S204" s="11"/>
@@ -11784,10 +11807,10 @@
     <row r="205" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="11"/>
       <c r="E205" s="3" t="s">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="F205" s="2">
-        <v>1984</v>
+        <v>1991</v>
       </c>
       <c r="G205" s="10"/>
       <c r="S205" s="11"/>
@@ -11809,10 +11832,10 @@
     <row r="206" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="11"/>
       <c r="E206" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F206" s="2">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="G206" s="10"/>
       <c r="S206" s="11"/>
@@ -11834,10 +11857,10 @@
     <row r="207" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="11"/>
       <c r="E207" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F207" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G207" s="10"/>
       <c r="S207" s="11"/>
@@ -11859,10 +11882,10 @@
     <row r="208" spans="4:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="11"/>
       <c r="E208" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F208" s="2">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="G208" s="10"/>
       <c r="S208" s="11"/>
@@ -11884,10 +11907,10 @@
     <row r="209" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D209" s="11"/>
       <c r="E209" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F209" s="2">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="G209" s="10"/>
       <c r="S209" s="11"/>
@@ -11909,10 +11932,10 @@
     <row r="210" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D210" s="11"/>
       <c r="E210" s="3" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="F210" s="2">
-        <v>2012</v>
+        <v>1984</v>
       </c>
       <c r="G210" s="10"/>
       <c r="S210" s="11"/>
@@ -11934,10 +11957,10 @@
     <row r="211" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="11"/>
       <c r="E211" s="3" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="F211" s="2">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="G211" s="10"/>
       <c r="S211" s="11"/>
@@ -11959,10 +11982,10 @@
     <row r="212" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="11"/>
       <c r="E212" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F212" s="2">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="G212" s="10"/>
       <c r="S212" s="11"/>
@@ -11984,10 +12007,10 @@
     <row r="213" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="11"/>
       <c r="E213" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F213" s="2">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="G213" s="10"/>
       <c r="S213" s="11"/>
@@ -12009,10 +12032,10 @@
     <row r="214" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="11"/>
       <c r="E214" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F214" s="2">
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="G214" s="10"/>
       <c r="S214" s="11"/>
@@ -12034,10 +12057,10 @@
     <row r="215" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="11"/>
       <c r="E215" s="3" t="s">
-        <v>212</v>
+        <v>34</v>
       </c>
       <c r="F215" s="2">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="G215" s="10"/>
       <c r="S215" s="11"/>
@@ -12059,10 +12082,10 @@
     <row r="216" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="11"/>
       <c r="E216" s="3" t="s">
-        <v>213</v>
+        <v>50</v>
       </c>
       <c r="F216" s="2">
-        <v>1989</v>
+        <v>2012</v>
       </c>
       <c r="G216" s="10"/>
       <c r="S216" s="11"/>
@@ -12084,10 +12107,10 @@
     <row r="217" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="11"/>
       <c r="E217" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F217" s="2">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="G217" s="10"/>
       <c r="S217" s="11"/>
@@ -12109,10 +12132,10 @@
     <row r="218" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="11"/>
       <c r="E218" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F218" s="2">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="G218" s="10"/>
       <c r="S218" s="11"/>
@@ -12134,10 +12157,10 @@
     <row r="219" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="11"/>
       <c r="E219" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F219" s="2">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="G219" s="10"/>
       <c r="S219" s="11"/>
@@ -12159,10 +12182,10 @@
     <row r="220" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="11"/>
       <c r="E220" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F220" s="2">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="G220" s="10"/>
       <c r="S220" s="11"/>
@@ -12184,10 +12207,10 @@
     <row r="221" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="11"/>
       <c r="E221" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F221" s="2">
-        <v>2012</v>
+        <v>1989</v>
       </c>
       <c r="G221" s="10"/>
       <c r="S221" s="11"/>
@@ -12209,10 +12232,10 @@
     <row r="222" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="11"/>
       <c r="E222" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F222" s="2">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="G222" s="10"/>
       <c r="S222" s="11"/>
@@ -12234,10 +12257,10 @@
     <row r="223" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="11"/>
       <c r="E223" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F223" s="2">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="G223" s="10"/>
       <c r="S223" s="11"/>
@@ -12259,10 +12282,10 @@
     <row r="224" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="11"/>
       <c r="E224" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F224" s="2">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="G224" s="10"/>
       <c r="S224" s="11"/>
@@ -12284,10 +12307,10 @@
     <row r="225" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D225" s="11"/>
       <c r="E225" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F225" s="2">
-        <v>2000</v>
+        <v>2013</v>
       </c>
       <c r="G225" s="10"/>
       <c r="S225" s="11"/>
@@ -12309,10 +12332,10 @@
     <row r="226" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D226" s="11"/>
       <c r="E226" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F226" s="2">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="G226" s="10"/>
       <c r="S226" s="11"/>
@@ -12334,10 +12357,10 @@
     <row r="227" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="11"/>
       <c r="E227" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F227" s="2">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="G227" s="10"/>
       <c r="S227" s="11"/>
@@ -12359,10 +12382,10 @@
     <row r="228" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="11"/>
       <c r="E228" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F228" s="2">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="G228" s="10"/>
       <c r="S228" s="11"/>
@@ -12384,10 +12407,10 @@
     <row r="229" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="11"/>
       <c r="E229" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F229" s="2">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="G229" s="10"/>
       <c r="S229" s="11"/>
@@ -12409,7 +12432,7 @@
     <row r="230" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D230" s="11"/>
       <c r="E230" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F230" s="2">
         <v>2000</v>
@@ -12434,10 +12457,10 @@
     <row r="231" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="11"/>
       <c r="E231" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F231" s="2">
-        <v>1993</v>
+        <v>2006</v>
       </c>
       <c r="G231" s="10"/>
       <c r="S231" s="11"/>
@@ -12459,10 +12482,10 @@
     <row r="232" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="11"/>
       <c r="E232" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F232" s="2">
-        <v>2004</v>
+        <v>2014</v>
       </c>
       <c r="G232" s="10"/>
       <c r="S232" s="11"/>
@@ -12484,7 +12507,7 @@
     <row r="233" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="11"/>
       <c r="E233" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F233" s="2">
         <v>2015</v>
@@ -12509,10 +12532,10 @@
     <row r="234" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="11"/>
       <c r="E234" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F234" s="2">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G234" s="10"/>
       <c r="S234" s="11"/>
@@ -12534,10 +12557,10 @@
     <row r="235" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="11"/>
       <c r="E235" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F235" s="2">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="G235" s="10"/>
       <c r="S235" s="11"/>
@@ -12559,10 +12582,10 @@
     <row r="236" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="11"/>
       <c r="E236" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F236" s="2">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="G236" s="10"/>
       <c r="S236" s="11"/>
@@ -12584,10 +12607,10 @@
     <row r="237" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="11"/>
       <c r="E237" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F237" s="2">
-        <v>2022</v>
+        <v>2004</v>
       </c>
       <c r="G237" s="10"/>
       <c r="S237" s="11"/>
@@ -12609,10 +12632,10 @@
     <row r="238" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="11"/>
       <c r="E238" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F238" s="2">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="G238" s="10"/>
       <c r="S238" s="11"/>
@@ -12634,10 +12657,10 @@
     <row r="239" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="11"/>
       <c r="E239" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F239" s="2">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="G239" s="10"/>
       <c r="S239" s="11"/>
@@ -12659,10 +12682,10 @@
     <row r="240" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="11"/>
       <c r="E240" s="3" t="s">
-        <v>91</v>
+        <v>232</v>
       </c>
       <c r="F240" s="2">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="G240" s="10"/>
       <c r="S240" s="11"/>
@@ -12684,10 +12707,10 @@
     <row r="241" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="11"/>
       <c r="E241" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F241" s="2">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="G241" s="10"/>
       <c r="S241" s="11"/>
@@ -12709,10 +12732,10 @@
     <row r="242" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="11"/>
       <c r="E242" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F242" s="2">
-        <v>1960</v>
+        <v>2022</v>
       </c>
       <c r="G242" s="10"/>
       <c r="S242" s="11"/>
@@ -12734,7 +12757,7 @@
     <row r="243" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="11"/>
       <c r="E243" s="3" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="F243" s="2">
         <v>2018</v>
@@ -12759,10 +12782,10 @@
     <row r="244" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="11"/>
       <c r="E244" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F244" s="2">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="G244" s="10"/>
       <c r="S244" s="11"/>
@@ -12784,10 +12807,10 @@
     <row r="245" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="11"/>
       <c r="E245" s="3" t="s">
-        <v>240</v>
+        <v>91</v>
       </c>
       <c r="F245" s="2">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="G245" s="10"/>
       <c r="S245" s="11"/>
@@ -12809,10 +12832,10 @@
     <row r="246" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="11"/>
       <c r="E246" s="3" t="s">
-        <v>40</v>
+        <v>237</v>
       </c>
       <c r="F246" s="2">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="G246" s="10"/>
       <c r="S246" s="11"/>
@@ -12834,10 +12857,10 @@
     <row r="247" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="11"/>
       <c r="E247" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F247" s="2">
-        <v>1994</v>
+        <v>1960</v>
       </c>
       <c r="G247" s="10"/>
       <c r="S247" s="11"/>
@@ -12859,10 +12882,10 @@
     <row r="248" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="11"/>
       <c r="E248" s="3" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="F248" s="2">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="G248" s="10"/>
       <c r="S248" s="11"/>
@@ -12884,10 +12907,10 @@
     <row r="249" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="11"/>
       <c r="E249" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F249" s="2">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="G249" s="10"/>
       <c r="S249" s="11"/>
@@ -12909,10 +12932,10 @@
     <row r="250" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="11"/>
       <c r="E250" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F250" s="2">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="G250" s="10"/>
       <c r="S250" s="11"/>
@@ -12934,10 +12957,10 @@
     <row r="251" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="11"/>
       <c r="E251" s="3" t="s">
-        <v>245</v>
+        <v>40</v>
       </c>
       <c r="F251" s="2">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="G251" s="10"/>
       <c r="S251" s="11"/>
@@ -12959,10 +12982,10 @@
     <row r="252" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="11"/>
       <c r="E252" s="3" t="s">
-        <v>44</v>
+        <v>241</v>
       </c>
       <c r="F252" s="2">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="G252" s="10"/>
       <c r="S252" s="11"/>
@@ -12976,7 +12999,7 @@
     <row r="253" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="11"/>
       <c r="E253" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F253" s="2">
         <v>2014</v>
@@ -12986,527 +13009,527 @@
     <row r="254" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="11"/>
       <c r="E254" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="F254" s="2">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="G254" s="10"/>
     </row>
     <row r="255" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="11"/>
       <c r="E255" s="3" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
       <c r="F255" s="2">
-        <v>2023</v>
+        <v>1999</v>
       </c>
       <c r="G255" s="10"/>
     </row>
     <row r="256" spans="4:25" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="11"/>
       <c r="E256" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F256" s="2">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="G256" s="10"/>
     </row>
     <row r="257" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="11"/>
       <c r="E257" s="3" t="s">
-        <v>248</v>
+        <v>44</v>
       </c>
       <c r="F257" s="2">
-        <v>2021</v>
+        <v>1992</v>
       </c>
       <c r="G257" s="10"/>
     </row>
     <row r="258" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="11"/>
       <c r="E258" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F258" s="2">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G258" s="10"/>
     </row>
     <row r="259" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="11"/>
       <c r="E259" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F259" s="2">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G259" s="10"/>
     </row>
     <row r="260" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="11"/>
       <c r="E260" s="3" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="F260" s="2">
-        <v>1968</v>
+        <v>2023</v>
       </c>
       <c r="G260" s="10"/>
     </row>
     <row r="261" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="11"/>
       <c r="E261" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F261" s="2">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="G261" s="10"/>
     </row>
     <row r="262" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="11"/>
       <c r="E262" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F262" s="2">
-        <v>1998</v>
+        <v>2021</v>
       </c>
       <c r="G262" s="10"/>
     </row>
     <row r="263" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="11"/>
       <c r="E263" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F263" s="2">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="G263" s="10"/>
     </row>
     <row r="264" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="11"/>
       <c r="E264" s="3" t="s">
-        <v>254</v>
+        <v>37</v>
       </c>
       <c r="F264" s="2">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="G264" s="10"/>
     </row>
     <row r="265" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="11"/>
       <c r="E265" s="3" t="s">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="F265" s="2">
-        <v>2023</v>
+        <v>1968</v>
       </c>
       <c r="G265" s="10"/>
     </row>
     <row r="266" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="11"/>
       <c r="E266" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F266" s="2">
-        <v>1998</v>
+        <v>2009</v>
       </c>
       <c r="G266" s="10"/>
     </row>
     <row r="267" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="11"/>
       <c r="E267" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F267" s="2">
-        <v>2023</v>
+        <v>1998</v>
       </c>
       <c r="G267" s="10"/>
     </row>
     <row r="268" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="11"/>
       <c r="E268" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="F268" s="2">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="G268" s="10"/>
     </row>
     <row r="269" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="11"/>
       <c r="E269" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F269" s="2">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G269" s="10"/>
     </row>
     <row r="270" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="11"/>
       <c r="E270" s="3" t="s">
-        <v>258</v>
+        <v>14</v>
       </c>
       <c r="F270" s="2">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="G270" s="10"/>
     </row>
     <row r="271" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="11"/>
       <c r="E271" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F271" s="2">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="G271" s="10"/>
     </row>
     <row r="272" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="11"/>
       <c r="E272" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F272" s="2">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="G272" s="10"/>
     </row>
     <row r="273" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="11"/>
       <c r="E273" s="3" t="s">
-        <v>261</v>
+        <v>49</v>
       </c>
       <c r="F273" s="2">
-        <v>2003</v>
+        <v>2016</v>
       </c>
       <c r="G273" s="10"/>
     </row>
     <row r="274" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="11"/>
       <c r="E274" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F274" s="2">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="G274" s="10"/>
     </row>
     <row r="275" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="11"/>
       <c r="E275" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F275" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="G275" s="10"/>
     </row>
     <row r="276" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="11"/>
       <c r="E276" s="3" t="s">
-        <v>12</v>
+        <v>259</v>
       </c>
       <c r="F276" s="2">
-        <v>2022</v>
+        <v>2006</v>
       </c>
       <c r="G276" s="10"/>
     </row>
     <row r="277" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="11"/>
       <c r="E277" s="3" t="s">
-        <v>2</v>
+        <v>260</v>
       </c>
       <c r="F277" s="2">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="G277" s="10"/>
     </row>
     <row r="278" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="11"/>
       <c r="E278" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F278" s="2">
-        <v>1981</v>
+        <v>2003</v>
       </c>
       <c r="G278" s="10"/>
     </row>
     <row r="279" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="11"/>
       <c r="E279" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F279" s="2">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="G279" s="10"/>
     </row>
     <row r="280" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="11"/>
       <c r="E280" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F280" s="2">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="G280" s="10"/>
     </row>
     <row r="281" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="11"/>
       <c r="E281" s="3" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="F281" s="2">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G281" s="10"/>
     </row>
     <row r="282" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="11"/>
       <c r="E282" s="3" t="s">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="F282" s="2">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="G282" s="10"/>
     </row>
     <row r="283" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="11"/>
       <c r="E283" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F283" s="2">
-        <v>2014</v>
+        <v>1981</v>
       </c>
       <c r="G283" s="10"/>
     </row>
     <row r="284" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="11"/>
       <c r="E284" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F284" s="2">
-        <v>2020</v>
+        <v>1996</v>
       </c>
       <c r="G284" s="10"/>
     </row>
     <row r="285" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="11"/>
       <c r="E285" s="3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F285" s="2">
-        <v>2008</v>
+        <v>2021</v>
       </c>
       <c r="G285" s="10"/>
     </row>
     <row r="286" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="11"/>
       <c r="E286" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F286" s="2">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="G286" s="10"/>
     </row>
     <row r="287" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="11"/>
       <c r="E287" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F287" s="2">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="G287" s="10"/>
     </row>
     <row r="288" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="11"/>
       <c r="E288" s="3" t="s">
-        <v>7</v>
+        <v>269</v>
       </c>
       <c r="F288" s="2">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="G288" s="10"/>
     </row>
     <row r="289" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="11"/>
       <c r="E289" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F289" s="2">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="G289" s="10"/>
     </row>
     <row r="290" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="11"/>
       <c r="E290" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F290" s="2">
-        <v>1995</v>
+        <v>2008</v>
       </c>
       <c r="G290" s="10"/>
     </row>
     <row r="291" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="11"/>
       <c r="E291" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F291" s="2">
-        <v>1971</v>
+        <v>2007</v>
       </c>
       <c r="G291" s="10"/>
     </row>
     <row r="292" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="11"/>
       <c r="E292" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F292" s="2">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="G292" s="10"/>
     </row>
     <row r="293" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="11"/>
       <c r="E293" s="3" t="s">
-        <v>278</v>
+        <v>7</v>
       </c>
       <c r="F293" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G293" s="10"/>
     </row>
     <row r="294" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="11"/>
       <c r="E294" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F294" s="2">
-        <v>1988</v>
+        <v>2009</v>
       </c>
       <c r="G294" s="10"/>
     </row>
     <row r="295" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="11"/>
       <c r="E295" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F295" s="2">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="G295" s="10"/>
     </row>
     <row r="296" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="11"/>
       <c r="E296" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F296" s="2">
-        <v>1982</v>
+        <v>1971</v>
       </c>
       <c r="G296" s="10"/>
     </row>
     <row r="297" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="11"/>
       <c r="E297" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F297" s="2">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="G297" s="10"/>
     </row>
     <row r="298" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="11"/>
       <c r="E298" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F298" s="2">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="G298" s="10"/>
     </row>
     <row r="299" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="11"/>
       <c r="E299" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F299" s="2">
-        <v>2015</v>
+        <v>1988</v>
       </c>
       <c r="G299" s="10"/>
     </row>
     <row r="300" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="11"/>
       <c r="E300" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F300" s="2">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="G300" s="10"/>
     </row>
     <row r="301" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="11"/>
       <c r="E301" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F301" s="2">
-        <v>2006</v>
+        <v>1982</v>
       </c>
       <c r="G301" s="10"/>
     </row>
     <row r="302" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="11"/>
       <c r="E302" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F302" s="2">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="G302" s="10"/>
     </row>
     <row r="303" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="11"/>
       <c r="E303" s="3" t="s">
-        <v>38</v>
+        <v>283</v>
       </c>
       <c r="F303" s="2">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="G303" s="10"/>
     </row>
     <row r="304" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="11"/>
       <c r="E304" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F304" s="2">
-        <v>1990</v>
+        <v>2015</v>
       </c>
       <c r="G304" s="10"/>
     </row>
     <row r="305" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="11"/>
       <c r="E305" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F305" s="2">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="G305" s="10"/>
     </row>
     <row r="306" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="11"/>
       <c r="E306" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F306" s="2">
         <v>2006</v>
@@ -13516,107 +13539,107 @@
     <row r="307" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="11"/>
       <c r="E307" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F307" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="G307" s="10"/>
     </row>
     <row r="308" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="11"/>
       <c r="E308" s="3" t="s">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="F308" s="2">
-        <v>1979</v>
+        <v>2019</v>
       </c>
       <c r="G308" s="10"/>
     </row>
     <row r="309" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="11"/>
       <c r="E309" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F309" s="2">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="G309" s="10"/>
     </row>
     <row r="310" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="11"/>
       <c r="E310" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F310" s="2">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="G310" s="10"/>
     </row>
     <row r="311" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="11"/>
       <c r="E311" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F311" s="2">
-        <v>1986</v>
+        <v>2006</v>
       </c>
       <c r="G311" s="10"/>
     </row>
     <row r="312" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="11"/>
       <c r="E312" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F312" s="2">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="G312" s="10"/>
     </row>
     <row r="313" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="11"/>
       <c r="E313" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F313" s="2">
-        <v>2014</v>
+        <v>1979</v>
       </c>
       <c r="G313" s="10"/>
     </row>
     <row r="314" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="11"/>
       <c r="E314" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="F314" s="2">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="G314" s="10"/>
     </row>
     <row r="315" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="11"/>
       <c r="E315" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F315" s="2">
-        <v>1992</v>
+        <v>2013</v>
       </c>
       <c r="G315" s="10"/>
     </row>
     <row r="316" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="11"/>
       <c r="E316" s="3" t="s">
-        <v>71</v>
+        <v>295</v>
       </c>
       <c r="F316" s="2">
-        <v>2007</v>
+        <v>1986</v>
       </c>
       <c r="G316" s="10"/>
     </row>
     <row r="317" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="11"/>
       <c r="E317" s="3" t="s">
-        <v>60</v>
+        <v>296</v>
       </c>
       <c r="F317" s="2">
         <v>2022</v>
@@ -13626,107 +13649,107 @@
     <row r="318" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="11"/>
       <c r="E318" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F318" s="2">
-        <v>1990</v>
+        <v>2014</v>
       </c>
       <c r="G318" s="10"/>
     </row>
     <row r="319" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="11"/>
       <c r="E319" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F319" s="2">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="G319" s="10"/>
     </row>
     <row r="320" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="11"/>
       <c r="E320" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F320" s="2">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="G320" s="10"/>
     </row>
     <row r="321" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="11"/>
       <c r="E321" s="3" t="s">
-        <v>303</v>
+        <v>71</v>
       </c>
       <c r="F321" s="2">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="G321" s="10"/>
     </row>
     <row r="322" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="11"/>
       <c r="E322" s="3" t="s">
-        <v>304</v>
+        <v>60</v>
       </c>
       <c r="F322" s="2">
-        <v>1975</v>
+        <v>2022</v>
       </c>
       <c r="G322" s="10"/>
     </row>
     <row r="323" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="11"/>
       <c r="E323" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="F323" s="2">
-        <v>2019</v>
+        <v>1990</v>
       </c>
       <c r="G323" s="10"/>
     </row>
     <row r="324" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="11"/>
       <c r="E324" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F324" s="2">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="G324" s="10"/>
     </row>
     <row r="325" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="11"/>
       <c r="E325" s="3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F325" s="2">
-        <v>1989</v>
+        <v>1982</v>
       </c>
       <c r="G325" s="10"/>
     </row>
     <row r="326" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="11"/>
       <c r="E326" s="3" t="s">
-        <v>85</v>
+        <v>303</v>
       </c>
       <c r="F326" s="2">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="G326" s="10"/>
     </row>
     <row r="327" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="11"/>
       <c r="E327" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F327" s="2">
-        <v>1993</v>
+        <v>1975</v>
       </c>
       <c r="G327" s="10"/>
     </row>
     <row r="328" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="11"/>
       <c r="E328" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F328" s="2">
         <v>2019</v>
@@ -13736,277 +13759,277 @@
     <row r="329" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="11"/>
       <c r="E329" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F329" s="2">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="G329" s="10"/>
     </row>
     <row r="330" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="11"/>
       <c r="E330" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F330" s="2">
-        <v>2009</v>
+        <v>1989</v>
       </c>
       <c r="G330" s="10"/>
     </row>
     <row r="331" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="11"/>
       <c r="E331" s="3" t="s">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="F331" s="2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G331" s="10"/>
     </row>
     <row r="332" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="11"/>
       <c r="E332" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F332" s="2">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="G332" s="10"/>
     </row>
     <row r="333" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="11"/>
       <c r="E333" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F333" s="2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="G333" s="10"/>
     </row>
     <row r="334" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="11"/>
       <c r="E334" s="3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F334" s="2">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="G334" s="10"/>
     </row>
     <row r="335" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="11"/>
       <c r="E335" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F335" s="2">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="G335" s="10"/>
     </row>
     <row r="336" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="11"/>
       <c r="E336" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F336" s="2">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="G336" s="10"/>
     </row>
     <row r="337" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="11"/>
       <c r="E337" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F337" s="2">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="G337" s="10"/>
     </row>
     <row r="338" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="11"/>
       <c r="E338" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F338" s="2">
-        <v>1997</v>
+        <v>2016</v>
       </c>
       <c r="G338" s="10"/>
     </row>
     <row r="339" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="11"/>
       <c r="E339" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F339" s="2">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="G339" s="10"/>
     </row>
     <row r="340" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="11"/>
       <c r="E340" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F340" s="2">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="G340" s="10"/>
     </row>
     <row r="341" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D341" s="11"/>
       <c r="E341" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F341" s="2">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G341" s="10"/>
     </row>
     <row r="342" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D342" s="11"/>
       <c r="E342" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F342" s="2">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="G342" s="10"/>
     </row>
     <row r="343" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D343" s="11"/>
       <c r="E343" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F343" s="2">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="G343" s="10"/>
     </row>
     <row r="344" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D344" s="11"/>
       <c r="E344" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F344" s="2">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="G344" s="10"/>
     </row>
     <row r="345" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D345" s="11"/>
       <c r="E345" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F345" s="2">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="G345" s="10"/>
     </row>
     <row r="346" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D346" s="11"/>
       <c r="E346" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F346" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G346" s="10"/>
     </row>
     <row r="347" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D347" s="11"/>
       <c r="E347" s="3" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="F347" s="2">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="G347" s="10"/>
     </row>
     <row r="348" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D348" s="11"/>
       <c r="E348" s="3" t="s">
-        <v>46</v>
+        <v>324</v>
       </c>
       <c r="F348" s="2">
-        <v>1999</v>
+        <v>2012</v>
       </c>
       <c r="G348" s="10"/>
     </row>
     <row r="349" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D349" s="11"/>
-      <c r="E349" s="4">
-        <v>1917</v>
+      <c r="E349" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="F349" s="2">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G349" s="10"/>
     </row>
     <row r="350" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D350" s="11"/>
       <c r="E350" s="3" t="s">
-        <v>97</v>
+        <v>326</v>
       </c>
       <c r="F350" s="2">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="G350" s="10"/>
     </row>
     <row r="351" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D351" s="11"/>
       <c r="E351" s="3" t="s">
-        <v>90</v>
+        <v>327</v>
       </c>
       <c r="F351" s="2">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="G351" s="10"/>
     </row>
     <row r="352" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D352" s="11"/>
       <c r="E352" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F352" s="2">
-        <v>2019</v>
+        <v>1999</v>
       </c>
       <c r="G352" s="10"/>
     </row>
     <row r="353" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D353" s="11"/>
       <c r="E353" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F353" s="2">
-        <v>2018</v>
+        <v>1999</v>
       </c>
       <c r="G353" s="10"/>
     </row>
     <row r="354" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D354" s="11"/>
-      <c r="E354" s="3" t="s">
-        <v>67</v>
+      <c r="E354" s="4">
+        <v>1917</v>
       </c>
       <c r="F354" s="2">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="G354" s="10"/>
     </row>
     <row r="355" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="11"/>
       <c r="E355" s="3" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="F355" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G355" s="10"/>
     </row>
     <row r="356" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="11"/>
       <c r="E356" s="3" t="s">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="F356" s="2">
         <v>2005</v>
@@ -14016,537 +14039,537 @@
     <row r="357" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="11"/>
       <c r="E357" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F357" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="G357" s="10"/>
     </row>
     <row r="358" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="11"/>
       <c r="E358" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F358" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G358" s="10"/>
     </row>
     <row r="359" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="11"/>
       <c r="E359" s="3" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="F359" s="2">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="G359" s="10"/>
     </row>
     <row r="360" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="11"/>
       <c r="E360" s="3" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="F360" s="2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G360" s="10"/>
     </row>
     <row r="361" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="11"/>
       <c r="E361" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F361" s="2">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="G361" s="10"/>
     </row>
     <row r="362" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D362" s="11"/>
       <c r="E362" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F362" s="2">
-        <v>1976</v>
+        <v>2020</v>
       </c>
       <c r="G362" s="10"/>
     </row>
     <row r="363" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="11"/>
       <c r="E363" s="3" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="F363" s="2">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="G363" s="10"/>
     </row>
     <row r="364" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="11"/>
       <c r="E364" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F364" s="2">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="G364" s="10"/>
     </row>
     <row r="365" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="11"/>
       <c r="E365" s="3" t="s">
-        <v>335</v>
+        <v>78</v>
       </c>
       <c r="F365" s="2">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G365" s="10"/>
     </row>
     <row r="366" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="11"/>
       <c r="E366" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F366" s="2">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="G366" s="10"/>
     </row>
     <row r="367" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="11"/>
       <c r="E367" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F367" s="2">
-        <v>2018</v>
+        <v>1976</v>
       </c>
       <c r="G367" s="10"/>
     </row>
     <row r="368" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="11"/>
       <c r="E368" s="3" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="F368" s="2">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="G368" s="10"/>
     </row>
     <row r="369" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D369" s="11"/>
       <c r="E369" s="3" t="s">
-        <v>338</v>
+        <v>31</v>
       </c>
       <c r="F369" s="2">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="G369" s="10"/>
     </row>
     <row r="370" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D370" s="11"/>
       <c r="E370" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F370" s="2">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="G370" s="10"/>
     </row>
     <row r="371" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D371" s="11"/>
       <c r="E371" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F371" s="2">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="G371" s="10"/>
     </row>
     <row r="372" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D372" s="11"/>
       <c r="E372" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F372" s="2">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="G372" s="10"/>
     </row>
     <row r="373" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D373" s="11"/>
       <c r="E373" s="3" t="s">
-        <v>342</v>
+        <v>26</v>
       </c>
       <c r="F373" s="2">
-        <v>1983</v>
+        <v>2013</v>
       </c>
       <c r="G373" s="10"/>
     </row>
     <row r="374" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D374" s="11"/>
       <c r="E374" s="3" t="s">
-        <v>68</v>
+        <v>338</v>
       </c>
       <c r="F374" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="G374" s="10"/>
     </row>
     <row r="375" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D375" s="11"/>
       <c r="E375" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F375" s="2">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="G375" s="10"/>
     </row>
     <row r="376" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D376" s="11"/>
       <c r="E376" s="3" t="s">
-        <v>69</v>
+        <v>340</v>
       </c>
       <c r="F376" s="2">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="G376" s="10"/>
     </row>
     <row r="377" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D377" s="11"/>
       <c r="E377" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F377" s="2">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="G377" s="10"/>
     </row>
     <row r="378" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D378" s="11"/>
       <c r="E378" s="3" t="s">
-        <v>62</v>
+        <v>342</v>
       </c>
       <c r="F378" s="2">
-        <v>2010</v>
+        <v>1983</v>
       </c>
       <c r="G378" s="10"/>
     </row>
     <row r="379" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D379" s="11"/>
       <c r="E379" s="3" t="s">
-        <v>345</v>
+        <v>68</v>
       </c>
       <c r="F379" s="2">
-        <v>1999</v>
+        <v>2009</v>
       </c>
       <c r="G379" s="10"/>
     </row>
     <row r="380" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D380" s="11"/>
       <c r="E380" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F380" s="2">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G380" s="10"/>
     </row>
     <row r="381" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D381" s="11"/>
       <c r="E381" s="3" t="s">
-        <v>347</v>
+        <v>69</v>
       </c>
       <c r="F381" s="2">
-        <v>1985</v>
+        <v>2002</v>
       </c>
       <c r="G381" s="10"/>
     </row>
     <row r="382" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D382" s="11"/>
       <c r="E382" s="3" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F382" s="2">
-        <v>2005</v>
+        <v>2015</v>
       </c>
       <c r="G382" s="10"/>
     </row>
     <row r="383" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D383" s="11"/>
       <c r="E383" s="3" t="s">
-        <v>349</v>
+        <v>62</v>
       </c>
       <c r="F383" s="2">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="G383" s="10"/>
     </row>
     <row r="384" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D384" s="11"/>
       <c r="E384" s="3" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="F384" s="2">
-        <v>2017</v>
+        <v>1999</v>
       </c>
       <c r="G384" s="10"/>
     </row>
     <row r="385" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D385" s="11"/>
       <c r="E385" s="3" t="s">
-        <v>32</v>
+        <v>346</v>
       </c>
       <c r="F385" s="2">
-        <v>2003</v>
+        <v>2019</v>
       </c>
       <c r="G385" s="10"/>
     </row>
     <row r="386" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D386" s="11"/>
       <c r="E386" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F386" s="2">
-        <v>1972</v>
+        <v>1985</v>
       </c>
       <c r="G386" s="10"/>
     </row>
     <row r="387" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D387" s="11"/>
       <c r="E387" s="3" t="s">
-        <v>65</v>
+        <v>348</v>
       </c>
       <c r="F387" s="2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="G387" s="10"/>
     </row>
     <row r="388" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D388" s="11"/>
       <c r="E388" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F388" s="2">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="G388" s="10"/>
     </row>
     <row r="389" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D389" s="11"/>
       <c r="E389" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F389" s="2">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G389" s="10"/>
     </row>
     <row r="390" spans="4:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D390" s="11"/>
       <c r="E390" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F390" s="2">
-        <v>2017</v>
+        <v>2003</v>
       </c>
       <c r="G390" s="10"/>
     </row>
     <row r="391" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D391" s="11"/>
       <c r="E391" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F391" s="2">
-        <v>2017</v>
-      </c>
-      <c r="G391" s="11"/>
+        <v>1972</v>
+      </c>
+      <c r="G391" s="10"/>
     </row>
     <row r="392" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D392" s="11"/>
       <c r="E392" s="3" t="s">
-        <v>355</v>
+        <v>65</v>
       </c>
       <c r="F392" s="2">
-        <v>2018</v>
-      </c>
-      <c r="G392" s="11"/>
+        <v>2007</v>
+      </c>
+      <c r="G392" s="10"/>
     </row>
     <row r="393" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D393" s="11"/>
       <c r="E393" s="3" t="s">
-        <v>39</v>
+        <v>352</v>
       </c>
       <c r="F393" s="2">
-        <v>2010</v>
-      </c>
-      <c r="G393" s="11"/>
+        <v>2011</v>
+      </c>
+      <c r="G393" s="10"/>
     </row>
     <row r="394" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D394" s="11"/>
       <c r="E394" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F394" s="2">
-        <v>2004</v>
-      </c>
-      <c r="G394" s="11"/>
+        <v>2022</v>
+      </c>
+      <c r="G394" s="10"/>
     </row>
     <row r="395" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D395" s="11"/>
       <c r="E395" s="3" t="s">
-        <v>357</v>
+        <v>18</v>
       </c>
       <c r="F395" s="2">
-        <v>1994</v>
-      </c>
-      <c r="G395" s="11"/>
+        <v>2017</v>
+      </c>
+      <c r="G395" s="10"/>
     </row>
     <row r="396" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D396" s="11"/>
       <c r="E396" s="3" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F396" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="G396" s="11"/>
     </row>
     <row r="397" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D397" s="11"/>
       <c r="E397" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F397" s="2">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="G397" s="11"/>
     </row>
     <row r="398" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D398" s="11"/>
       <c r="E398" s="3" t="s">
-        <v>360</v>
+        <v>39</v>
       </c>
       <c r="F398" s="2">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="G398" s="11"/>
     </row>
     <row r="399" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D399" s="11"/>
       <c r="E399" s="3" t="s">
-        <v>6</v>
+        <v>356</v>
       </c>
       <c r="F399" s="2">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="G399" s="11"/>
     </row>
     <row r="400" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D400" s="11"/>
       <c r="E400" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F400" s="2">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="G400" s="11"/>
     </row>
     <row r="401" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D401" s="11"/>
       <c r="E401" s="3" t="s">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="F401" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="G401" s="11"/>
     </row>
     <row r="402" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D402" s="11"/>
       <c r="E402" s="3" t="s">
-        <v>29</v>
+        <v>359</v>
       </c>
       <c r="F402" s="2">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="G402" s="11"/>
     </row>
     <row r="403" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D403" s="11"/>
       <c r="E403" s="3" t="s">
-        <v>76</v>
+        <v>360</v>
       </c>
       <c r="F403" s="2">
-        <v>2005</v>
+        <v>1990</v>
       </c>
       <c r="G403" s="11"/>
     </row>
     <row r="404" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D404" s="11"/>
       <c r="E404" s="3" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F404" s="2">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="G404" s="11"/>
     </row>
     <row r="405" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D405" s="11"/>
       <c r="E405" s="3" t="s">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="F405" s="2">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="G405" s="11"/>
     </row>
     <row r="406" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D406" s="11"/>
       <c r="E406" s="3" t="s">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="F406" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G406" s="11"/>
     </row>
     <row r="407" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D407" s="11"/>
       <c r="E407" s="3" t="s">
-        <v>363</v>
+        <v>29</v>
       </c>
       <c r="F407" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G407" s="11"/>
     </row>
     <row r="408" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D408" s="11"/>
       <c r="E408" s="3" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F408" s="2">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="G408" s="11"/>
     </row>
     <row r="409" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D409" s="11"/>
       <c r="E409" s="3" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F409" s="2">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="G409" s="11"/>
     </row>
     <row r="410" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D410" s="11"/>
       <c r="E410" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F410" s="2">
         <v>2002</v>
@@ -14556,437 +14579,437 @@
     <row r="411" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D411" s="11"/>
       <c r="E411" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F411" s="2">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="G411" s="11"/>
     </row>
     <row r="412" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D412" s="11"/>
       <c r="E412" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F412" s="2">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="G412" s="11"/>
     </row>
     <row r="413" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D413" s="11"/>
       <c r="E413" s="3" t="s">
-        <v>366</v>
+        <v>15</v>
       </c>
       <c r="F413" s="2">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="G413" s="11"/>
     </row>
     <row r="414" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D414" s="11"/>
       <c r="E414" s="3" t="s">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="F414" s="2">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="G414" s="11"/>
     </row>
     <row r="415" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D415" s="11"/>
       <c r="E415" s="3" t="s">
-        <v>368</v>
+        <v>96</v>
       </c>
       <c r="F415" s="2">
-        <v>1980</v>
+        <v>2002</v>
       </c>
       <c r="G415" s="11"/>
     </row>
     <row r="416" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D416" s="11"/>
       <c r="E416" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F416" s="2">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="G416" s="11"/>
     </row>
     <row r="417" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D417" s="11"/>
       <c r="E417" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="F417" s="2">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="G417" s="11"/>
     </row>
     <row r="418" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D418" s="11"/>
       <c r="E418" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F418" s="2">
-        <v>2004</v>
+        <v>2017</v>
       </c>
       <c r="G418" s="11"/>
     </row>
     <row r="419" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D419" s="11"/>
       <c r="E419" s="3" t="s">
-        <v>42</v>
+        <v>367</v>
       </c>
       <c r="F419" s="2">
-        <v>1993</v>
+        <v>2014</v>
       </c>
       <c r="G419" s="11"/>
     </row>
     <row r="420" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D420" s="11"/>
       <c r="E420" s="3" t="s">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="F420" s="2">
-        <v>2017</v>
+        <v>1980</v>
       </c>
       <c r="G420" s="11"/>
     </row>
     <row r="421" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D421" s="11"/>
       <c r="E421" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F421" s="2">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="G421" s="11"/>
     </row>
     <row r="422" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D422" s="11"/>
       <c r="E422" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F422" s="2">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="G422" s="11"/>
     </row>
     <row r="423" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D423" s="11"/>
       <c r="E423" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F423" s="2">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="G423" s="11"/>
     </row>
     <row r="424" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D424" s="11"/>
       <c r="E424" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F424" s="2">
-        <v>2016</v>
+        <v>1993</v>
       </c>
       <c r="G424" s="11"/>
     </row>
     <row r="425" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D425" s="11"/>
       <c r="E425" s="3" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="F425" s="2">
-        <v>1994</v>
+        <v>2017</v>
       </c>
       <c r="G425" s="11"/>
     </row>
     <row r="426" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D426" s="11"/>
       <c r="E426" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F426" s="2">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="G426" s="11"/>
     </row>
     <row r="427" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D427" s="11"/>
       <c r="E427" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F427" s="2">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="G427" s="11"/>
     </row>
     <row r="428" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D428" s="11"/>
       <c r="E428" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F428" s="2">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="G428" s="11"/>
     </row>
     <row r="429" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D429" s="11"/>
       <c r="E429" s="3" t="s">
-        <v>378</v>
+        <v>28</v>
       </c>
       <c r="F429" s="2">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="G429" s="11"/>
     </row>
     <row r="430" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D430" s="11"/>
       <c r="E430" s="3" t="s">
-        <v>379</v>
+        <v>8</v>
       </c>
       <c r="F430" s="2">
-        <v>2004</v>
+        <v>1994</v>
       </c>
       <c r="G430" s="11"/>
     </row>
     <row r="431" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D431" s="11"/>
       <c r="E431" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F431" s="2">
-        <v>2001</v>
+        <v>2015</v>
       </c>
       <c r="G431" s="11"/>
     </row>
     <row r="432" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D432" s="11"/>
       <c r="E432" s="3" t="s">
-        <v>56</v>
+        <v>376</v>
       </c>
       <c r="F432" s="2">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="G432" s="11"/>
     </row>
     <row r="433" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D433" s="11"/>
       <c r="E433" s="3" t="s">
-        <v>88</v>
+        <v>377</v>
       </c>
       <c r="F433" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G433" s="11"/>
     </row>
     <row r="434" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D434" s="11"/>
       <c r="E434" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F434" s="2">
-        <v>1985</v>
+        <v>2001</v>
       </c>
       <c r="G434" s="11"/>
     </row>
     <row r="435" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D435" s="11"/>
       <c r="E435" s="3" t="s">
-        <v>72</v>
+        <v>379</v>
       </c>
       <c r="F435" s="2">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="G435" s="11"/>
     </row>
     <row r="436" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D436" s="11"/>
       <c r="E436" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F436" s="2">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="G436" s="11"/>
     </row>
     <row r="437" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D437" s="11"/>
       <c r="E437" s="3" t="s">
-        <v>383</v>
+        <v>56</v>
       </c>
       <c r="F437" s="2">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="G437" s="11"/>
     </row>
     <row r="438" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D438" s="11"/>
       <c r="E438" s="3" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="F438" s="2">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="G438" s="11"/>
     </row>
     <row r="439" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D439" s="11"/>
       <c r="E439" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F439" s="2">
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="G439" s="11"/>
     </row>
     <row r="440" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D440" s="11"/>
       <c r="E440" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F440" s="2">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="G440" s="11"/>
     </row>
     <row r="441" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D441" s="11"/>
       <c r="E441" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F441" s="2">
-        <v>1977</v>
+        <v>2003</v>
       </c>
       <c r="G441" s="11"/>
     </row>
     <row r="442" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D442" s="11"/>
       <c r="E442" s="3" t="s">
-        <v>4</v>
+        <v>383</v>
       </c>
       <c r="F442" s="2">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="G442" s="11"/>
     </row>
     <row r="443" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D443" s="11"/>
       <c r="E443" s="3" t="s">
-        <v>386</v>
+        <v>3</v>
       </c>
       <c r="F443" s="2">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="G443" s="11"/>
     </row>
     <row r="444" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D444" s="11"/>
       <c r="E444" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F444" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="G444" s="11"/>
     </row>
     <row r="445" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D445" s="11"/>
       <c r="E445" s="3" t="s">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="F445" s="2">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="G445" s="11"/>
     </row>
     <row r="446" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D446" s="11"/>
       <c r="E446" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F446" s="2">
-        <v>2014</v>
+        <v>1977</v>
       </c>
       <c r="G446" s="11"/>
     </row>
     <row r="447" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D447" s="11"/>
       <c r="E447" s="3" t="s">
-        <v>390</v>
+        <v>4</v>
       </c>
       <c r="F447" s="2">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="G447" s="11"/>
     </row>
     <row r="448" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D448" s="11"/>
       <c r="E448" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="F448" s="2">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G448" s="11"/>
     </row>
     <row r="449" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D449" s="11"/>
       <c r="E449" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F449" s="2">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="G449" s="11"/>
     </row>
     <row r="450" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D450" s="11"/>
       <c r="E450" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="F450" s="2">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="G450" s="11"/>
     </row>
     <row r="451" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D451" s="11"/>
       <c r="E451" s="3" t="s">
-        <v>66</v>
+        <v>389</v>
       </c>
       <c r="F451" s="2">
-        <v>2003</v>
+        <v>2014</v>
       </c>
       <c r="G451" s="11"/>
     </row>
     <row r="452" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D452" s="11"/>
       <c r="E452" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F452" s="2">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="G452" s="11"/>
     </row>
     <row r="453" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D453" s="11"/>
       <c r="E453" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F453" s="2">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="G453" s="11"/>
     </row>
     <row r="454" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D454" s="11"/>
       <c r="E454" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F454" s="2">
         <v>2017</v>
@@ -14996,107 +15019,107 @@
     <row r="455" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D455" s="11"/>
       <c r="E455" s="3" t="s">
-        <v>1</v>
+        <v>393</v>
       </c>
       <c r="F455" s="2">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="G455" s="11"/>
     </row>
     <row r="456" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D456" s="11"/>
       <c r="E456" s="3" t="s">
-        <v>397</v>
+        <v>66</v>
       </c>
       <c r="F456" s="2">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="G456" s="11"/>
     </row>
     <row r="457" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D457" s="11"/>
       <c r="E457" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F457" s="2">
-        <v>1980</v>
+        <v>2012</v>
       </c>
       <c r="G457" s="11"/>
     </row>
     <row r="458" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D458" s="11"/>
       <c r="E458" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F458" s="2">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="G458" s="11"/>
     </row>
     <row r="459" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D459" s="11"/>
       <c r="E459" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F459" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="G459" s="11"/>
     </row>
     <row r="460" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D460" s="11"/>
       <c r="E460" s="3" t="s">
-        <v>401</v>
+        <v>1</v>
       </c>
       <c r="F460" s="2">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="G460" s="11"/>
     </row>
     <row r="461" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D461" s="11"/>
       <c r="E461" s="3" t="s">
-        <v>89</v>
+        <v>397</v>
       </c>
       <c r="F461" s="2">
-        <v>2015</v>
+        <v>1995</v>
       </c>
       <c r="G461" s="11"/>
     </row>
     <row r="462" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D462" s="11"/>
       <c r="E462" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F462" s="2">
-        <v>2016</v>
+        <v>1980</v>
       </c>
       <c r="G462" s="11"/>
     </row>
     <row r="463" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D463" s="11"/>
       <c r="E463" s="3" t="s">
-        <v>10</v>
+        <v>399</v>
       </c>
       <c r="F463" s="2">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="G463" s="11"/>
     </row>
     <row r="464" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D464" s="11"/>
       <c r="E464" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F464" s="2">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="G464" s="11"/>
     </row>
     <row r="465" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D465" s="11"/>
       <c r="E465" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F465" s="2">
         <v>2009</v>
@@ -15106,57 +15129,57 @@
     <row r="466" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D466" s="11"/>
       <c r="E466" s="3" t="s">
-        <v>405</v>
+        <v>89</v>
       </c>
       <c r="F466" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="G466" s="11"/>
     </row>
     <row r="467" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D467" s="11"/>
       <c r="E467" s="3" t="s">
-        <v>17</v>
+        <v>402</v>
       </c>
       <c r="F467" s="2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="G467" s="11"/>
     </row>
     <row r="468" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D468" s="11"/>
       <c r="E468" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F468" s="2">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="G468" s="11"/>
     </row>
     <row r="469" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D469" s="11"/>
       <c r="E469" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F469" s="2">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="G469" s="11"/>
     </row>
     <row r="470" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D470" s="11"/>
       <c r="E470" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F470" s="2">
-        <v>1994</v>
+        <v>2009</v>
       </c>
       <c r="G470" s="11"/>
     </row>
     <row r="471" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D471" s="11"/>
       <c r="E471" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F471" s="2">
         <v>2014</v>
@@ -15166,86 +15189,136 @@
     <row r="472" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D472" s="11"/>
       <c r="E472" s="3" t="s">
-        <v>409</v>
+        <v>17</v>
       </c>
       <c r="F472" s="2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G472" s="11"/>
     </row>
     <row r="473" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D473" s="11"/>
       <c r="E473" s="3" t="s">
-        <v>410</v>
+        <v>5</v>
       </c>
       <c r="F473" s="2">
-        <v>1999</v>
+        <v>2018</v>
       </c>
       <c r="G473" s="11"/>
     </row>
     <row r="474" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D474" s="11"/>
       <c r="E474" s="3" t="s">
-        <v>41</v>
+        <v>406</v>
       </c>
       <c r="F474" s="2">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="G474" s="11"/>
     </row>
     <row r="475" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D475" s="11"/>
       <c r="E475" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F475" s="2">
-        <v>2019</v>
+        <v>1994</v>
       </c>
       <c r="G475" s="11"/>
     </row>
     <row r="476" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D476" s="11"/>
       <c r="E476" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F476" s="2">
-        <v>1994</v>
+        <v>2014</v>
       </c>
       <c r="G476" s="11"/>
     </row>
     <row r="477" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D477" s="11"/>
       <c r="E477" s="3" t="s">
-        <v>51</v>
+        <v>409</v>
       </c>
       <c r="F477" s="2">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="G477" s="11"/>
     </row>
     <row r="478" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D478" s="11"/>
       <c r="E478" s="3" t="s">
-        <v>95</v>
+        <v>410</v>
       </c>
       <c r="F478" s="2">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="G478" s="11"/>
     </row>
     <row r="479" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D479" s="11"/>
-      <c r="E479" s="31"/>
-      <c r="F479" s="31"/>
+      <c r="E479" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F479" s="2">
+        <v>2019</v>
+      </c>
       <c r="G479" s="11"/>
+    </row>
+    <row r="480" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D480" s="11"/>
+      <c r="E480" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F480" s="2">
+        <v>2019</v>
+      </c>
+      <c r="G480" s="11"/>
+    </row>
+    <row r="481" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D481" s="11"/>
+      <c r="E481" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F481" s="2">
+        <v>1994</v>
+      </c>
+      <c r="G481" s="11"/>
+    </row>
+    <row r="482" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D482" s="11"/>
+      <c r="E482" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F482" s="2">
+        <v>2008</v>
+      </c>
+      <c r="G482" s="11"/>
+    </row>
+    <row r="483" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D483" s="11"/>
+      <c r="E483" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F483" s="2">
+        <v>2010</v>
+      </c>
+      <c r="G483" s="11"/>
+    </row>
+    <row r="484" spans="4:7" x14ac:dyDescent="0.2">
+      <c r="D484" s="11"/>
+      <c r="E484" s="30"/>
+      <c r="F484" s="30"/>
+      <c r="G484" s="11"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N3:O15">
     <sortCondition sortBy="icon" ref="N2:N15"/>
   </sortState>
-  <conditionalFormatting sqref="E2:F1048576">
+  <conditionalFormatting sqref="E7:F1048576">
     <cfRule type="notContainsBlanks" dxfId="5" priority="2">
-      <formula>LEN(TRIM(E2))&gt;0</formula>
+      <formula>LEN(TRIM(E7))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I1048576">

--- a/spreadsheets/lists.xlsx
+++ b/spreadsheets/lists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41497923-CA4F-A84A-94E9-BD6BE22ECE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E200235A-5521-F943-9B90-D360BEADC62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{98AF27AA-E156-FB4B-94CA-68D339A0B8C2}"/>
   </bookViews>
